--- a/SE202526/Management/Gantt Chart.xlsx
+++ b/SE202526/Management/Gantt Chart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\SE2526_66565_67196_67215_68509_68663_70116\SE202526\Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilh\Documents\Universidade\ES\Projeto\SE2526_66565_67196_67215_68509_68663_70116\SE202526\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CC57CC-B373-4C4E-8B0E-0CD1D7D853E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A90DDCD-B70D-4967-B6C3-08816692DB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Planner" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,19 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Project Planner'!$3:$4</definedName>
     <definedName name="TitleRegion..BO60">'Project Planner'!$C$3:$C$4</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -236,13 +247,13 @@
     <t>Plan upgrades for user stories</t>
   </si>
   <si>
-    <t>Implementing</t>
-  </si>
-  <si>
-    <t>Review code and document</t>
-  </si>
-  <si>
     <t>p</t>
+  </si>
+  <si>
+    <t>Implement User Stories 1 and 2</t>
+  </si>
+  <si>
+    <t>Review code and documentation</t>
   </si>
 </sst>
 </file>
@@ -569,98 +580,98 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyBorder="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="7" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="13" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="14" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="15" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="9" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="3" xfId="10">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="11" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="5" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="4" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="12" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="18" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="8" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="17" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="17" applyBorder="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="17" applyBorder="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="16" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="7" applyBorder="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="13" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="14" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="15" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="9" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="6" borderId="3" xfId="10">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="11" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="5" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="4" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="12" applyBorder="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="18" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="8" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -1107,379 +1118,379 @@
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="50.5" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="6" customWidth="1"/>
-    <col min="4" max="7" width="11.6640625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" style="8" customWidth="1"/>
-    <col min="9" max="28" width="3.25" style="7"/>
+    <col min="3" max="3" width="15.6640625" style="1" customWidth="1"/>
+    <col min="4" max="7" width="11.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="3" customWidth="1"/>
+    <col min="9" max="28" width="3.25" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:68" ht="60" customHeight="1" x14ac:dyDescent="1.2">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="2:68" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="12" t="s">
+      <c r="C2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="8">
         <v>22</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="5" t="s">
+      <c r="K2" s="9"/>
+      <c r="L2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="5" t="s">
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="5" t="s">
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="17"/>
-      <c r="AB2" s="5" t="s">
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="18"/>
-      <c r="AJ2" s="4" t="s">
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="AK2" s="4"/>
-      <c r="AL2" s="4"/>
-      <c r="AM2" s="4"/>
-      <c r="AN2" s="4"/>
-      <c r="AO2" s="4"/>
-      <c r="AP2" s="4"/>
-      <c r="AQ2" s="4"/>
-    </row>
-    <row r="3" spans="2:68" s="19" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+    </row>
+    <row r="3" spans="2:68" s="14" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="21"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20" t="s">
+      <c r="J3" s="16"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20" t="s">
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="20"/>
-      <c r="Z3" s="22" t="s">
+      <c r="X3" s="15"/>
+      <c r="Z3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AD3" s="20" t="s">
+      <c r="AD3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="AJ3" s="20"/>
-      <c r="AK3" s="20" t="s">
+      <c r="AJ3" s="15"/>
+      <c r="AK3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="AL3" s="20"/>
-      <c r="AM3" s="20"/>
-      <c r="AN3" s="22" t="s">
+      <c r="AL3" s="15"/>
+      <c r="AM3" s="15"/>
+      <c r="AN3" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AO3" s="20"/>
-      <c r="AQ3" s="20"/>
-      <c r="AR3" s="20" t="s">
+      <c r="AO3" s="15"/>
+      <c r="AQ3" s="15"/>
+      <c r="AR3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="AS3" s="20"/>
-      <c r="AT3" s="20"/>
-      <c r="AU3" s="20"/>
-      <c r="AV3" s="20"/>
-      <c r="AX3" s="20"/>
-      <c r="AY3" s="20" t="s">
+      <c r="AS3" s="15"/>
+      <c r="AT3" s="15"/>
+      <c r="AU3" s="15"/>
+      <c r="AV3" s="15"/>
+      <c r="AX3" s="15"/>
+      <c r="AY3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AZ3" s="20"/>
-      <c r="BA3" s="20"/>
-      <c r="BB3" s="20"/>
-      <c r="BC3" s="20"/>
-      <c r="BE3" s="20"/>
-      <c r="BF3" s="20" t="s">
+      <c r="AZ3" s="15"/>
+      <c r="BA3" s="15"/>
+      <c r="BB3" s="15"/>
+      <c r="BC3" s="15"/>
+      <c r="BE3" s="15"/>
+      <c r="BF3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="BG3" s="20"/>
-      <c r="BH3" s="20"/>
-      <c r="BI3" s="20"/>
-      <c r="BJ3" s="20"/>
-      <c r="BK3" s="20"/>
-      <c r="BL3" s="20"/>
-      <c r="BM3" s="20"/>
-      <c r="BN3" s="22" t="s">
+      <c r="BG3" s="15"/>
+      <c r="BH3" s="15"/>
+      <c r="BI3" s="15"/>
+      <c r="BJ3" s="15"/>
+      <c r="BK3" s="15"/>
+      <c r="BL3" s="15"/>
+      <c r="BM3" s="15"/>
+      <c r="BN3" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="2:68" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="23">
-        <v>1</v>
-      </c>
-      <c r="J4" s="23">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="18">
+        <v>1</v>
+      </c>
+      <c r="J4" s="18">
         <v>2</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="18">
         <v>3</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="18">
         <v>4</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="18">
         <v>5</v>
       </c>
-      <c r="N4" s="23">
+      <c r="N4" s="18">
         <v>6</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="18">
         <v>7</v>
       </c>
-      <c r="P4" s="23">
+      <c r="P4" s="18">
         <v>8</v>
       </c>
-      <c r="Q4" s="23">
+      <c r="Q4" s="18">
         <v>9</v>
       </c>
-      <c r="R4" s="23">
+      <c r="R4" s="18">
         <v>10</v>
       </c>
-      <c r="S4" s="23">
+      <c r="S4" s="18">
         <v>11</v>
       </c>
-      <c r="T4" s="23">
+      <c r="T4" s="18">
         <v>12</v>
       </c>
-      <c r="U4" s="23">
+      <c r="U4" s="18">
         <v>13</v>
       </c>
-      <c r="V4" s="23">
+      <c r="V4" s="18">
         <v>14</v>
       </c>
-      <c r="W4" s="23">
+      <c r="W4" s="18">
         <v>15</v>
       </c>
-      <c r="X4" s="23">
+      <c r="X4" s="18">
         <v>16</v>
       </c>
-      <c r="Y4" s="23">
+      <c r="Y4" s="18">
         <v>17</v>
       </c>
-      <c r="Z4" s="23">
+      <c r="Z4" s="18">
         <v>18</v>
       </c>
-      <c r="AA4" s="23">
+      <c r="AA4" s="18">
         <v>19</v>
       </c>
-      <c r="AB4" s="23">
+      <c r="AB4" s="18">
         <v>20</v>
       </c>
-      <c r="AC4" s="23">
+      <c r="AC4" s="18">
         <v>21</v>
       </c>
-      <c r="AD4" s="23">
+      <c r="AD4" s="18">
         <v>22</v>
       </c>
-      <c r="AE4" s="23">
+      <c r="AE4" s="18">
         <v>23</v>
       </c>
-      <c r="AF4" s="23">
+      <c r="AF4" s="18">
         <v>24</v>
       </c>
-      <c r="AG4" s="23">
+      <c r="AG4" s="18">
         <v>25</v>
       </c>
-      <c r="AH4" s="23">
+      <c r="AH4" s="18">
         <v>26</v>
       </c>
-      <c r="AI4" s="23">
+      <c r="AI4" s="18">
         <v>27</v>
       </c>
-      <c r="AJ4" s="23">
+      <c r="AJ4" s="18">
         <v>28</v>
       </c>
-      <c r="AK4" s="23">
+      <c r="AK4" s="18">
         <v>29</v>
       </c>
-      <c r="AL4" s="23">
+      <c r="AL4" s="18">
         <v>30</v>
       </c>
-      <c r="AM4" s="23">
+      <c r="AM4" s="18">
         <v>31</v>
       </c>
-      <c r="AN4" s="23">
+      <c r="AN4" s="18">
         <v>32</v>
       </c>
-      <c r="AO4" s="23">
+      <c r="AO4" s="18">
         <v>33</v>
       </c>
-      <c r="AP4" s="23">
+      <c r="AP4" s="18">
         <v>34</v>
       </c>
-      <c r="AQ4" s="23">
+      <c r="AQ4" s="18">
         <v>35</v>
       </c>
-      <c r="AR4" s="23">
+      <c r="AR4" s="18">
         <v>36</v>
       </c>
-      <c r="AS4" s="23">
+      <c r="AS4" s="18">
         <v>37</v>
       </c>
-      <c r="AT4" s="23">
+      <c r="AT4" s="18">
         <v>38</v>
       </c>
-      <c r="AU4" s="23">
+      <c r="AU4" s="18">
         <v>39</v>
       </c>
-      <c r="AV4" s="23">
+      <c r="AV4" s="18">
         <v>40</v>
       </c>
-      <c r="AW4" s="23">
+      <c r="AW4" s="18">
         <v>41</v>
       </c>
-      <c r="AX4" s="23">
+      <c r="AX4" s="18">
         <v>42</v>
       </c>
-      <c r="AY4" s="23">
+      <c r="AY4" s="18">
         <v>43</v>
       </c>
-      <c r="AZ4" s="23">
+      <c r="AZ4" s="18">
         <v>44</v>
       </c>
-      <c r="BA4" s="23">
+      <c r="BA4" s="18">
         <v>45</v>
       </c>
-      <c r="BB4" s="23">
+      <c r="BB4" s="18">
         <v>46</v>
       </c>
-      <c r="BC4" s="23">
+      <c r="BC4" s="18">
         <v>47</v>
       </c>
-      <c r="BD4" s="23">
+      <c r="BD4" s="18">
         <v>48</v>
       </c>
-      <c r="BE4" s="23">
+      <c r="BE4" s="18">
         <v>49</v>
       </c>
-      <c r="BF4" s="23">
+      <c r="BF4" s="18">
         <v>50</v>
       </c>
-      <c r="BG4" s="23">
+      <c r="BG4" s="18">
         <v>51</v>
       </c>
-      <c r="BH4" s="23">
+      <c r="BH4" s="18">
         <v>52</v>
       </c>
-      <c r="BI4" s="23">
+      <c r="BI4" s="18">
         <v>53</v>
       </c>
-      <c r="BJ4" s="23">
+      <c r="BJ4" s="18">
         <v>54</v>
       </c>
-      <c r="BK4" s="23">
+      <c r="BK4" s="18">
         <v>55</v>
       </c>
-      <c r="BL4" s="23">
+      <c r="BL4" s="18">
         <v>56</v>
       </c>
-      <c r="BM4" s="23">
+      <c r="BM4" s="18">
         <v>57</v>
       </c>
-      <c r="BN4" s="23">
+      <c r="BN4" s="18">
         <v>58</v>
       </c>
-      <c r="BO4" s="23">
+      <c r="BO4" s="18">
         <v>59</v>
       </c>
-      <c r="BP4" s="23">
+      <c r="BP4" s="18">
         <v>60</v>
       </c>
     </row>
     <row r="5" spans="2:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="26">
-        <v>1</v>
-      </c>
-      <c r="E5" s="26">
+      <c r="D5" s="21">
+        <v>1</v>
+      </c>
+      <c r="E5" s="21">
         <v>6</v>
       </c>
-      <c r="F5" s="26">
-        <v>1</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="F5" s="21">
+        <v>1</v>
+      </c>
+      <c r="G5" s="21">
         <v>7</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1487,22 +1498,22 @@
       <c r="B6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="26">
-        <v>1</v>
-      </c>
-      <c r="E6" s="26">
+      <c r="D6" s="21">
+        <v>1</v>
+      </c>
+      <c r="E6" s="21">
         <v>6</v>
       </c>
-      <c r="F6" s="26">
-        <v>1</v>
-      </c>
-      <c r="G6" s="26">
+      <c r="F6" s="21">
+        <v>1</v>
+      </c>
+      <c r="G6" s="21">
         <v>7</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1510,45 +1521,45 @@
       <c r="B7">
         <v>67215.685089999999</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="26">
-        <v>1</v>
-      </c>
-      <c r="E7" s="26">
+      <c r="D7" s="21">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21">
         <v>6</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="21">
         <v>2</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="21">
         <v>6</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="21">
         <v>6</v>
       </c>
-      <c r="E8" s="26">
-        <v>1</v>
-      </c>
-      <c r="F8" s="26">
+      <c r="E8" s="21">
+        <v>1</v>
+      </c>
+      <c r="F8" s="21">
         <v>7</v>
       </c>
-      <c r="G8" s="26">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8">
+      <c r="G8" s="21">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1556,22 +1567,22 @@
       <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="21">
         <v>6</v>
       </c>
-      <c r="E9" s="26">
-        <v>1</v>
-      </c>
-      <c r="F9" s="26">
+      <c r="E9" s="21">
+        <v>1</v>
+      </c>
+      <c r="F9" s="21">
         <v>7</v>
       </c>
-      <c r="G9" s="26">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="G9" s="21">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1579,45 +1590,45 @@
       <c r="B10">
         <v>67215.685089999999</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="21">
         <v>6</v>
       </c>
-      <c r="E10" s="26">
-        <v>1</v>
-      </c>
-      <c r="F10" s="26">
+      <c r="E10" s="21">
+        <v>1</v>
+      </c>
+      <c r="F10" s="21">
         <v>7</v>
       </c>
-      <c r="G10" s="26">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="G10" s="21">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="21">
         <v>8</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="21">
         <v>4</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="21">
         <v>11</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="21">
         <v>3</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1625,22 +1636,22 @@
       <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="21">
         <v>12</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="21">
         <v>2</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="21">
         <v>13</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="21">
         <v>2</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="3">
         <v>0.4</v>
       </c>
     </row>
@@ -1648,208 +1659,208 @@
       <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="21">
         <v>14</v>
       </c>
-      <c r="E13" s="26">
-        <v>1</v>
-      </c>
-      <c r="F13" s="26">
+      <c r="E13" s="21">
+        <v>1</v>
+      </c>
+      <c r="F13" s="21">
         <v>0</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="21">
         <v>0</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="24"/>
-      <c r="C14" s="29" t="s">
+      <c r="B14" s="19"/>
+      <c r="C14" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="25">
         <v>14</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="25">
         <v>9</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="2">
         <v>15</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="2">
         <v>9</v>
       </c>
-      <c r="H14" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:68" ht="29" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="21">
         <v>23</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="21">
         <v>2</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="21">
         <v>24</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="21">
         <v>3</v>
       </c>
-      <c r="H15" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:68" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:68" ht="29" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="26">
+      <c r="C16" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="21">
         <v>25</v>
       </c>
-      <c r="E16" s="26">
-        <v>4</v>
-      </c>
-      <c r="F16" s="26">
-        <v>26</v>
-      </c>
-      <c r="G16" s="26">
-        <v>5</v>
-      </c>
-      <c r="H16" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E16" s="21">
+        <v>7</v>
+      </c>
+      <c r="F16" s="21">
+        <v>27</v>
+      </c>
+      <c r="G16" s="21">
+        <v>9</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:43" ht="29" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="26">
-        <v>29</v>
-      </c>
-      <c r="E17" s="26">
-        <v>1</v>
-      </c>
-      <c r="F17" s="26">
+      <c r="C17" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="21">
+        <v>32</v>
+      </c>
+      <c r="E17" s="21">
+        <v>2</v>
+      </c>
+      <c r="F17" s="21">
         <v>0</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="21">
         <v>0</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C18" s="31"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C19" s="31"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C20" s="31"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
       <c r="AQ20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C21" s="31"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
     </row>
     <row r="22" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C22" s="31"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
     </row>
     <row r="23" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C23" s="31"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
     </row>
     <row r="24" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C24" s="31"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="25" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C25" s="31"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C26" s="31"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
     </row>
     <row r="27" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C27" s="31"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
     </row>
     <row r="28" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C28" s="31"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
     </row>
     <row r="29" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C29" s="31"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
     </row>
     <row r="30" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C30" s="31"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -1970,7 +1981,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.34722222222222199" header="0.511811023622047" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter differentFirst="1">
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
   </headerFooter>

--- a/SE202526/Management/Gantt Chart.xlsx
+++ b/SE202526/Management/Gantt Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilh\Documents\Universidade\ES\Projeto\SE2526_66565_67196_67215_68509_68663_70116\SE202526\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A90DDCD-B70D-4967-B6C3-08816692DB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCBE1FD-2EAF-43DF-A508-9C088AE2A985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t>Project Planner</t>
   </si>
@@ -247,13 +247,13 @@
     <t>Plan upgrades for user stories</t>
   </si>
   <si>
-    <t>p</t>
-  </si>
-  <si>
     <t>Implement User Stories 1 and 2</t>
   </si>
   <si>
-    <t>Review code and documentation</t>
+    <t>Review code and create documentation for the first two User Stories</t>
+  </si>
+  <si>
+    <t>Implement User Story 3</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1118,7 @@
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="50.5" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="59.9140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="11.6640625" style="2" customWidth="1"/>
     <col min="8" max="8" width="15.6640625" style="3" customWidth="1"/>
     <col min="9" max="28" width="3.25" style="2"/>
@@ -1699,7 +1699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:68" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:68" ht="17" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>34</v>
       </c>
@@ -1722,12 +1722,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:68" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:68" ht="17" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" s="21">
         <v>25</v>
@@ -1745,12 +1745,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:43" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="17" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="21">
         <v>32</v>
@@ -1765,97 +1765,110 @@
         <v>0</v>
       </c>
       <c r="H17" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="21">
+        <v>32</v>
+      </c>
+      <c r="E18" s="21">
+        <v>2</v>
+      </c>
+      <c r="F18" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C18" s="26"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-    </row>
-    <row r="19" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G18" s="21">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="26"/>
       <c r="D19" s="21"/>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21"/>
     </row>
-    <row r="20" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="26"/>
       <c r="D20" s="21"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
-      <c r="AQ20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="26"/>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
     </row>
-    <row r="22" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="26"/>
       <c r="D22" s="21"/>
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
     </row>
-    <row r="23" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="26"/>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
     </row>
-    <row r="24" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="26"/>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
       <c r="G24" s="21"/>
     </row>
-    <row r="25" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="26"/>
       <c r="D25" s="21"/>
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
       <c r="G25" s="21"/>
     </row>
-    <row r="26" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="26"/>
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
       <c r="G26" s="21"/>
     </row>
-    <row r="27" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="26"/>
       <c r="D27" s="21"/>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
     </row>
-    <row r="28" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="26"/>
       <c r="D28" s="21"/>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
     </row>
-    <row r="29" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="26"/>
       <c r="D29" s="21"/>
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21"/>
     </row>
-    <row r="30" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="26"/>
       <c r="D30" s="21"/>
       <c r="E30" s="21"/>
